--- a/artfynd/A 3421-2021 artfynd.xlsx
+++ b/artfynd/A 3421-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119769617</v>
+        <v>119774947</v>
       </c>
       <c r="B2" t="n">
-        <v>91494</v>
+        <v>103418</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,44 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nederberga, Dlr</t>
+          <t>Nederberga, Nederberga, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484873</v>
+        <v>484817</v>
       </c>
       <c r="R2" t="n">
-        <v>6782205</v>
+        <v>6782177</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,14 +748,19 @@
           <t>2024-09-15</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>riklig och spridda i hela kalkbarrskogen</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -906,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119774947</v>
+        <v>119769617</v>
       </c>
       <c r="B4" t="n">
-        <v>103418</v>
+        <v>91494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,37 +919,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nederberga, Nederberga, Dlr</t>
+          <t>Nederberga, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484817</v>
+        <v>484873</v>
       </c>
       <c r="R4" t="n">
-        <v>6782177</v>
+        <v>6782205</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,19 +983,14 @@
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>18:23</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>18:23</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>riklig och spridda i hela kalkbarrskogen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,6 +999,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3421-2021 artfynd.xlsx
+++ b/artfynd/A 3421-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119774947</v>
+        <v>119769826</v>
       </c>
       <c r="B2" t="n">
-        <v>103418</v>
+        <v>100171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nederberga, Nederberga, Dlr</t>
+          <t>Nederberga, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484817</v>
+        <v>484873</v>
       </c>
       <c r="R2" t="n">
-        <v>6782177</v>
+        <v>6782205</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +756,14 @@
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>18:23</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18:23</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>rikligt spridd i området. Ej räknad, uppskattat</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119769826</v>
+        <v>119774947</v>
       </c>
       <c r="B3" t="n">
-        <v>100171</v>
+        <v>103418</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,45 +807,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nederberga, Dlr</t>
+          <t>Nederberga, Nederberga, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484873</v>
+        <v>484817</v>
       </c>
       <c r="R3" t="n">
-        <v>6782205</v>
+        <v>6782177</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,14 +864,19 @@
           <t>2024-09-15</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>rikligt spridd i området. Ej räknad, uppskattat</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3421-2021 artfynd.xlsx
+++ b/artfynd/A 3421-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119769826</v>
+        <v>119769617</v>
       </c>
       <c r="B2" t="n">
-        <v>100171</v>
+        <v>91512</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -763,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>rikligt spridd i området. Ej räknad, uppskattat</t>
+          <t>riklig och spridda i hela kalkbarrskogen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +793,7 @@
         <v>119774947</v>
       </c>
       <c r="B3" t="n">
-        <v>103418</v>
+        <v>103441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -903,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119769617</v>
+        <v>119769826</v>
       </c>
       <c r="B4" t="n">
-        <v>91494</v>
+        <v>100194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,30 +918,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>riklig och spridda i hela kalkbarrskogen</t>
+          <t>rikligt spridd i området. Ej räknad, uppskattat</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1021,7 @@
         <v>119776404</v>
       </c>
       <c r="B5" t="n">
-        <v>97813</v>
+        <v>97836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 3421-2021 artfynd.xlsx
+++ b/artfynd/A 3421-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119769617</v>
+        <v>119769826</v>
       </c>
       <c r="B2" t="n">
-        <v>91512</v>
+        <v>100194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -762,7 +763,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>riklig och spridda i hela kalkbarrskogen</t>
+          <t>rikligt spridd i området. Ej räknad, uppskattat</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119774947</v>
+        <v>119769617</v>
       </c>
       <c r="B3" t="n">
-        <v>103441</v>
+        <v>91512</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,37 +807,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nederberga, Nederberga, Dlr</t>
+          <t>Nederberga, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484817</v>
+        <v>484873</v>
       </c>
       <c r="R3" t="n">
-        <v>6782177</v>
+        <v>6782205</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,19 +871,14 @@
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>18:23</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>18:23</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>riklig och spridda i hela kalkbarrskogen</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,6 +887,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119769826</v>
+        <v>119774947</v>
       </c>
       <c r="B4" t="n">
-        <v>100194</v>
+        <v>103441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,45 +922,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nederberga, Dlr</t>
+          <t>Nederberga, Nederberga, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484873</v>
+        <v>484817</v>
       </c>
       <c r="R4" t="n">
-        <v>6782205</v>
+        <v>6782177</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,14 +979,19 @@
           <t>2024-09-15</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>rikligt spridd i området. Ej räknad, uppskattat</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +1000,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3421-2021 artfynd.xlsx
+++ b/artfynd/A 3421-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,6 +1131,132 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126199032</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98247</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>504</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nederberga, Nederberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>484912</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6782165</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>20 blommor</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3421-2021 artfynd.xlsx
+++ b/artfynd/A 3421-2021 artfynd.xlsx
@@ -1136,7 +1136,7 @@
         <v>126199032</v>
       </c>
       <c r="B6" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3421-2021 artfynd.xlsx
+++ b/artfynd/A 3421-2021 artfynd.xlsx
@@ -1136,7 +1136,7 @@
         <v>126199032</v>
       </c>
       <c r="B6" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3421-2021 artfynd.xlsx
+++ b/artfynd/A 3421-2021 artfynd.xlsx
@@ -1136,7 +1136,7 @@
         <v>126199032</v>
       </c>
       <c r="B6" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3421-2021 artfynd.xlsx
+++ b/artfynd/A 3421-2021 artfynd.xlsx
@@ -1136,7 +1136,7 @@
         <v>126199032</v>
       </c>
       <c r="B6" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3421-2021 artfynd.xlsx
+++ b/artfynd/A 3421-2021 artfynd.xlsx
@@ -1136,7 +1136,7 @@
         <v>126199032</v>
       </c>
       <c r="B6" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
